--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_20.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_20.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Diagnosis</t>
+          <t>HoursSleep</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>DV</t>
+          <t>IV</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.6031280749955596</v>
+        <v>-2.133121538749478</v>
       </c>
       <c r="C2">
-        <v>0.06331361091224338</v>
+        <v>0.4290673824328808</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-1.165160703277013</v>
+        <v>-0.5665444066983298</v>
       </c>
       <c r="C3">
-        <v>-0.2927663651315938</v>
+        <v>-0.02342951856970746</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-2.157249595172518</v>
+        <v>0.188683403325489</v>
       </c>
       <c r="C4">
-        <v>-0.7226457424434025</v>
+        <v>-0.1591356674992157</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.171362310152491</v>
+        <v>0.2732784841818003</v>
       </c>
       <c r="C5">
-        <v>1.094899601579485</v>
+        <v>-0.7679122015890557</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-1.234108091218612</v>
+        <v>-0.2936997150169786</v>
       </c>
       <c r="C6">
-        <v>-0.7524340672861534</v>
+        <v>0.4532043818202864</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.6095255496202997</v>
+        <v>-0.0406218641899854</v>
       </c>
       <c r="C7">
-        <v>-0.267764386200543</v>
+        <v>-0.005323822379210294</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.0980396428487047</v>
+        <v>-1.682764613345336</v>
       </c>
       <c r="C8">
-        <v>0.436730628541621</v>
+        <v>1.09925053129226</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.04245073065732731</v>
+        <v>-0.1496836779157268</v>
       </c>
       <c r="C9">
-        <v>-0.610411393028444</v>
+        <v>-0.6621757422582496</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.4524970774074731</v>
+        <v>0.2266755668871952</v>
       </c>
       <c r="C10">
-        <v>-0.03673723984324079</v>
+        <v>-0.4058017250273235</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-1.260246338749266</v>
+        <v>1.793576249659887</v>
       </c>
       <c r="C11">
-        <v>-0.209872530728659</v>
+        <v>0.3524703035214639</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.006786412283149864</v>
+        <v>0.3107827719667742</v>
       </c>
       <c r="C12">
-        <v>-0.7405419556596061</v>
+        <v>2.262829319092801</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.5133790630440048</v>
+        <v>-0.5902994808364461</v>
       </c>
       <c r="C13">
-        <v>0.01401966292062654</v>
+        <v>-0.1184957209771005</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-1.745969213683203</v>
+        <v>-0.2127874929320482</v>
       </c>
       <c r="C14">
-        <v>-0.5430312714155237</v>
+        <v>-0.7113628107308136</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-1.606627602823372</v>
+        <v>-1.064934997727123</v>
       </c>
       <c r="C15">
-        <v>0.442337142963426</v>
+        <v>2.315652102245292</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.1301799505240701</v>
+        <v>0.3306299801049181</v>
       </c>
       <c r="C16">
-        <v>0.6435080622892495</v>
+        <v>0.1849900659653309</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.255686243057729</v>
+        <v>0.5192095078736144</v>
       </c>
       <c r="C17">
-        <v>2.694947817893677</v>
+        <v>0.4811101528272149</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.076236149879913</v>
+        <v>-2.032219097037498</v>
       </c>
       <c r="C18">
-        <v>0.7577602884320329</v>
+        <v>1.663888474798485</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.1249641865397188</v>
+        <v>0.3516300278692941</v>
       </c>
       <c r="C19">
-        <v>0.3969996624175691</v>
+        <v>0.2282124196286147</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.07450793983130949</v>
+        <v>0.3423605384231693</v>
       </c>
       <c r="C20">
-        <v>-0.03734101065502397</v>
+        <v>0.638046667825002</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.3029429171197503</v>
+        <v>-0.6690417695515462</v>
       </c>
       <c r="C21">
-        <v>-0.2312395142637352</v>
+        <v>0.7116826018981777</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.6558828302674888</v>
+        <v>0.223501549541117</v>
       </c>
       <c r="C22">
-        <v>-0.07868271548937678</v>
+        <v>0.02192964811699535</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-1.050079374444574</v>
+        <v>-0.9224582447941855</v>
       </c>
       <c r="C23">
-        <v>1.516574215580138</v>
+        <v>-1.901839495489909</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.1196091167392034</v>
+        <v>1.369555160317328</v>
       </c>
       <c r="C24">
-        <v>0.525298764717216</v>
+        <v>-0.8811905396827884</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.813100470858242</v>
+        <v>-0.01117418989968727</v>
       </c>
       <c r="C25">
-        <v>1.061963336212264</v>
+        <v>-0.2384506204883573</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-1.878508759982926</v>
+        <v>0.6923507271151071</v>
       </c>
       <c r="C26">
-        <v>-0.3086770084313175</v>
+        <v>-1.166624007984392</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.7401237061570943</v>
+        <v>-2.213925053897145</v>
       </c>
       <c r="C27">
-        <v>-0.1093094087713253</v>
+        <v>0.5502719665299867</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.7193442373888453</v>
+        <v>1.467925816767518</v>
       </c>
       <c r="C28">
-        <v>-0.9859437341430871</v>
+        <v>0.8440154395132541</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.6133914524369248</v>
+        <v>-0.4947879373041293</v>
       </c>
       <c r="C29">
-        <v>-0.9696255041750744</v>
+        <v>-0.8041240346302009</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.2181868776109695</v>
+        <v>0.03932926882735867</v>
       </c>
       <c r="C30">
-        <v>-0.09026801230091222</v>
+        <v>-1.019569768832046</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.2142188155822175</v>
+        <v>0.5282745737453992</v>
       </c>
       <c r="C31">
-        <v>0.9434150869153127</v>
+        <v>-0.8711612351040277</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.09583894387133148</v>
+        <v>0.02814066617116358</v>
       </c>
       <c r="C32">
-        <v>0.3979043538590681</v>
+        <v>-0.8038513001007528</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-1.798869959335187</v>
+        <v>-0.2155967454879318</v>
       </c>
       <c r="C33">
-        <v>-1.872482816478416</v>
+        <v>-1.458992999207253</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>1.958844737206898</v>
+        <v>0.7944787838569948</v>
       </c>
       <c r="C34">
-        <v>1.807989586567788</v>
+        <v>-2.964160338379417</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.513893003688396</v>
+        <v>0.07201058041980331</v>
       </c>
       <c r="C35">
-        <v>-2.353768630366074</v>
+        <v>-0.161460996435997</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.2489189920087946</v>
+        <v>-0.3082848502814363</v>
       </c>
       <c r="C36">
-        <v>0.8605622866596416</v>
+        <v>0.9465905932172701</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>1.628726003105614</v>
+        <v>0.8271519397957436</v>
       </c>
       <c r="C37">
-        <v>-0.5491416931866715</v>
+        <v>-1.368447048900097</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.7158932309287845</v>
+        <v>0.4400629055771734</v>
       </c>
       <c r="C38">
-        <v>-2.322089398801094</v>
+        <v>0.3157072708357698</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>2.482125067094067</v>
+        <v>-0.4482449781460512</v>
       </c>
       <c r="C39">
-        <v>0.7107484514981888</v>
+        <v>0.1241327342798608</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.547907607217614</v>
+        <v>0.01645557009186173</v>
       </c>
       <c r="C40">
-        <v>0.5888507215614216</v>
+        <v>0.8058593804241551</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.3232410187450748</v>
+        <v>0.5090192199601596</v>
       </c>
       <c r="C41">
-        <v>0.286188250430679</v>
+        <v>-0.49153078881115</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.9922491914987654</v>
+        <v>-2.028283539661686</v>
       </c>
       <c r="C42">
-        <v>-0.831071090513299</v>
+        <v>0.879432267434749</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.2003418089677195</v>
+        <v>1.148712995550415</v>
       </c>
       <c r="C43">
-        <v>2.292052101551807</v>
+        <v>0.5012834187073107</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.8200030458430196</v>
+        <v>-0.8038711706997144</v>
       </c>
       <c r="C44">
-        <v>1.759730781385847</v>
+        <v>1.669539649879778</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.05968555689429387</v>
+        <v>-0.80804540484224</v>
       </c>
       <c r="C45">
-        <v>-0.5296484771286322</v>
+        <v>2.540685656045783</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-1.553814743653276</v>
+        <v>0.5157189675334836</v>
       </c>
       <c r="C46">
-        <v>0.427947132309538</v>
+        <v>0.3423433462430571</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.5402438989714147</v>
+        <v>-1.273969702817193</v>
       </c>
       <c r="C47">
-        <v>-0.7705595828911627</v>
+        <v>1.456228754420628</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.7565227754798342</v>
+        <v>-0.08670360688987713</v>
       </c>
       <c r="C48">
-        <v>-1.309539782651155</v>
+        <v>-0.1619355033949566</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.2561398959907918</v>
+        <v>0.9883651092071977</v>
       </c>
       <c r="C49">
-        <v>1.407626800086599</v>
+        <v>-0.3367580771644781</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>1.994258350657494</v>
+        <v>-0.02355779372910194</v>
       </c>
       <c r="C50">
-        <v>1.827157951384406</v>
+        <v>0.0953803561079192</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.04023848342613249</v>
+        <v>-0.07598210695604025</v>
       </c>
       <c r="C51">
-        <v>0.04124872472507991</v>
+        <v>-0.4676593344918164</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>1.508679978533704</v>
+        <v>0.385414127972596</v>
       </c>
       <c r="C52">
-        <v>-0.07517782569363052</v>
+        <v>-0.1810467227435945</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.02322263475239041</v>
+        <v>1.089503072956223</v>
       </c>
       <c r="C53">
-        <v>1.890079689761442</v>
+        <v>-0.05823205036531687</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>1.609359889366721</v>
+        <v>-0.7905044795538919</v>
       </c>
       <c r="C54">
-        <v>1.976012657168943</v>
+        <v>0.09360717498820589</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.4246143619442581</v>
+        <v>1.761627697841086</v>
       </c>
       <c r="C55">
-        <v>-0.6026258665930894</v>
+        <v>-0.0250855022637787</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>-1.069662665276867</v>
+        <v>-0.5764915011835092</v>
       </c>
       <c r="C56">
-        <v>-1.841402181488419</v>
+        <v>0.9874523292285473</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>1.22612421065476</v>
+        <v>1.152662877706051</v>
       </c>
       <c r="C57">
-        <v>-0.6033522831203966</v>
+        <v>0.6850963389761915</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.3618987161026099</v>
+        <v>1.641594070637143</v>
       </c>
       <c r="C58">
-        <v>-0.2354155477588697</v>
+        <v>-0.4402884310817732</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.118415003387304</v>
+        <v>-0.9149459339628468</v>
       </c>
       <c r="C59">
-        <v>1.107191269699951</v>
+        <v>0.2456322597919061</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.5672254806410314</v>
+        <v>1.474620622411167</v>
       </c>
       <c r="C60">
-        <v>-0.3763343964719417</v>
+        <v>-0.01208522920031718</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.541904305691239</v>
+        <v>0.3531062759073432</v>
       </c>
       <c r="C61">
-        <v>1.307879181434642</v>
+        <v>0.05613277250224824</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>-1.812512035929316</v>
+        <v>-1.3310395791744</v>
       </c>
       <c r="C62">
-        <v>-0.3364242761947246</v>
+        <v>1.403797851405348</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>-0.3134144788905284</v>
+        <v>-0.2996551638711902</v>
       </c>
       <c r="C63">
-        <v>0.6217824034740553</v>
+        <v>-0.1754259038160795</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.01222720636212585</v>
+        <v>-0.8736537828195138</v>
       </c>
       <c r="C64">
-        <v>-1.658000871686101</v>
+        <v>1.166072728562187</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.3334631110048815</v>
+        <v>-0.4492118157733478</v>
       </c>
       <c r="C65">
-        <v>-1.083763953001998</v>
+        <v>0.8242718144072347</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>-1.918829552911193</v>
+        <v>0.9777041730764346</v>
       </c>
       <c r="C66">
-        <v>-1.554737582590322</v>
+        <v>-0.4314545851891561</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>-0.04370048561222921</v>
+        <v>0.2397425428704001</v>
       </c>
       <c r="C67">
-        <v>-1.001273898617022</v>
+        <v>-0.4353392706409558</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>1.705729630008106</v>
+        <v>1.328619252585046</v>
       </c>
       <c r="C68">
-        <v>0.7956863429034428</v>
+        <v>0.7404817087607752</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.2081186469274128</v>
+        <v>0.07183405745063398</v>
       </c>
       <c r="C69">
-        <v>-0.9893466298545439</v>
+        <v>0.01937354265840539</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>1.647701924336124</v>
+        <v>1.435572709685497</v>
       </c>
       <c r="C70">
-        <v>0.252717478326412</v>
+        <v>0.8509672316667167</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.035399043531317</v>
+        <v>-1.74138358196925</v>
       </c>
       <c r="C71">
-        <v>0.649774942171591</v>
+        <v>1.743786410127468</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-0.5626242278677211</v>
+        <v>0.9693321722878019</v>
       </c>
       <c r="C72">
-        <v>0.506330894895448</v>
+        <v>-0.2174308027633987</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.251045771954153</v>
+        <v>0.3000294457863781</v>
       </c>
       <c r="C73">
-        <v>-0.03867758749624847</v>
+        <v>-0.4334639255254883</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.1835223807214021</v>
+        <v>0.1732458020060752</v>
       </c>
       <c r="C74">
-        <v>0.2882064678437204</v>
+        <v>-0.5781521058216477</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>1.519980675663697</v>
+        <v>1.313545387480661</v>
       </c>
       <c r="C75">
-        <v>-0.9473359950915254</v>
+        <v>0.1422283363793677</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.08453244098434459</v>
+        <v>1.900934404541854</v>
       </c>
       <c r="C76">
-        <v>0.6386199812687063</v>
+        <v>-0.1038053956980463</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>-1.018260707180052</v>
+        <v>-1.887325277865066</v>
       </c>
       <c r="C77">
-        <v>-0.4487826033854043</v>
+        <v>0.9214865271270946</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>-1.448470629771607</v>
+        <v>1.157860543807822</v>
       </c>
       <c r="C78">
-        <v>0.7136976892766462</v>
+        <v>-0.2962646105383968</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>-0.01138987020425773</v>
+        <v>-1.09702872856984</v>
       </c>
       <c r="C79">
-        <v>-1.234984653970188</v>
+        <v>-0.8874383270098121</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>-0.6021226735894122</v>
+        <v>-1.464306501513601</v>
       </c>
       <c r="C80">
-        <v>1.346406023155969</v>
+        <v>1.503363822584997</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>2.34958988409769</v>
+        <v>-1.867822032669641</v>
       </c>
       <c r="C81">
-        <v>-0.5078427090958051</v>
+        <v>1.137155405114974</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>-1.555232568154427</v>
+        <v>-0.8912414820497196</v>
       </c>
       <c r="C82">
-        <v>-1.209764227724834</v>
+        <v>1.50778279364626</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.3598947574529703</v>
+        <v>1.049430555383508</v>
       </c>
       <c r="C83">
-        <v>1.151938841604764</v>
+        <v>-0.9276935023592159</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-0.2318461529941559</v>
+        <v>-0.2429473614797956</v>
       </c>
       <c r="C84">
-        <v>-0.7270225777340898</v>
+        <v>-0.7349694092811911</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>-0.1879925188743428</v>
+        <v>0.4941304459717364</v>
       </c>
       <c r="C85">
-        <v>1.890648241600228</v>
+        <v>0.1034928416697661</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>-0.6733177752484119</v>
+        <v>0.9138041899892619</v>
       </c>
       <c r="C86">
-        <v>0.1945103117601693</v>
+        <v>-1.12310499318954</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.3479443728452018</v>
+        <v>0.7645129466371655</v>
       </c>
       <c r="C87">
-        <v>-1.162490885005112</v>
+        <v>1.422227501304012</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-0.2099001301702067</v>
+        <v>-0.4873651990295834</v>
       </c>
       <c r="C88">
-        <v>-2.137210744565631</v>
+        <v>0.9969100294640005</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>0.08769934505439769</v>
+        <v>0.2846154505463714</v>
       </c>
       <c r="C89">
-        <v>0.1640926385700415</v>
+        <v>-0.3086768947607043</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>-0.60467148562935</v>
+        <v>-1.024219029090214</v>
       </c>
       <c r="C90">
-        <v>-2.640356850782929</v>
+        <v>0.1760470097398343</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.03166704000187091</v>
+        <v>0.8173387180248876</v>
       </c>
       <c r="C91">
-        <v>0.7051858446171911</v>
+        <v>-0.1782038505244182</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.314059607458719</v>
+        <v>0.3417806556075121</v>
       </c>
       <c r="C92">
-        <v>0.03629100362375155</v>
+        <v>0.8086512223970241</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.7527757151296086</v>
+        <v>0.3266171012269157</v>
       </c>
       <c r="C93">
-        <v>0.7581874393083994</v>
+        <v>0.246445299379745</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.1927143404092963</v>
+        <v>0.968944758682654</v>
       </c>
       <c r="C94">
-        <v>-0.1674375977667036</v>
+        <v>-1.176460609408849</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>2.667251934933348</v>
+        <v>1.403536448500519</v>
       </c>
       <c r="C95">
-        <v>0.5135491729269377</v>
+        <v>-0.309906788264466</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.4749601201842194</v>
+        <v>0.5265217087007316</v>
       </c>
       <c r="C96">
-        <v>0.5631823656910946</v>
+        <v>0.1057538111202252</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-1.917762481027068</v>
+        <v>0.2664445108411348</v>
       </c>
       <c r="C97">
-        <v>0.2307862024403395</v>
+        <v>-0.4274066630170354</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>-0.06758200158316868</v>
+        <v>0.8079149027770444</v>
       </c>
       <c r="C98">
-        <v>-0.7244276264387363</v>
+        <v>-1.360909894150413</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>1.40751377031496</v>
+        <v>1.574874254743742</v>
       </c>
       <c r="C99">
-        <v>0.5155384609922455</v>
+        <v>-0.6629050566670912</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.5617588025628509</v>
+        <v>2.204181614726036</v>
       </c>
       <c r="C100">
-        <v>-0.8101281852772947</v>
+        <v>0.1399629071912849</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,1310 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.5597457281757356</v>
+        <v>-0.05916452448455709</v>
       </c>
       <c r="C101">
-        <v>-0.7835202970555191</v>
+        <v>-1.259828703925327</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>0.52055477298016</v>
+      </c>
+      <c r="C102">
+        <v>-0.6654506092322786</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>-0.5995612628466378</v>
+      </c>
+      <c r="C103">
+        <v>-1.374176496239288</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>0.4500819177443254</v>
+      </c>
+      <c r="C104">
+        <v>1.293690957364739</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>-0.8521002002885953</v>
+      </c>
+      <c r="C105">
+        <v>-0.12528936635387</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>0.09335610795492458</v>
+      </c>
+      <c r="C106">
+        <v>0.09815502293001899</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>0.6780386571370272</v>
+      </c>
+      <c r="C107">
+        <v>0.02221531549499367</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-0.3872489639675564</v>
+      </c>
+      <c r="C108">
+        <v>-0.3037737154905126</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>0.5082798826514149</v>
+      </c>
+      <c r="C109">
+        <v>-1.99403105899351</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-1.242108005677071</v>
+      </c>
+      <c r="C110">
+        <v>0.8426993694850688</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.64286314107183</v>
+      </c>
+      <c r="C111">
+        <v>-1.064418185028996</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.4510621994834352</v>
+      </c>
+      <c r="C112">
+        <v>-0.3769886780714929</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>-1.522533583051642</v>
+      </c>
+      <c r="C113">
+        <v>0.4262281410993964</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-0.4100618341394999</v>
+      </c>
+      <c r="C114">
+        <v>-0.5504315474493703</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>1.730641363358439</v>
+      </c>
+      <c r="C115">
+        <v>-1.025153617926318</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>1.366455462539967</v>
+      </c>
+      <c r="C116">
+        <v>-0.9730609828394019</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-0.6761414939774444</v>
+      </c>
+      <c r="C117">
+        <v>0.1270667193587226</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>-0.7787068108581833</v>
+      </c>
+      <c r="C118">
+        <v>1.427443840202192</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>0.03385507691476213</v>
+      </c>
+      <c r="C119">
+        <v>-0.6245864068260455</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>-0.4381634698929799</v>
+      </c>
+      <c r="C120">
+        <v>0.1502187008101446</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>-0.4877597821020429</v>
+      </c>
+      <c r="C121">
+        <v>-0.4890832988595594</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>0.01322535480494802</v>
+      </c>
+      <c r="C122">
+        <v>1.325404338499029</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>-0.07422046942763769</v>
+      </c>
+      <c r="C123">
+        <v>-1.632300707729957</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>0.1064995738026037</v>
+      </c>
+      <c r="C124">
+        <v>1.318896241963124</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0.4011183148551722</v>
+      </c>
+      <c r="C125">
+        <v>1.206664992771944</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>-0.5553168233509299</v>
+      </c>
+      <c r="C126">
+        <v>0.7325628805437068</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>-0.5576359543375636</v>
+      </c>
+      <c r="C127">
+        <v>2.055992169120896</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>0.08841672306820353</v>
+      </c>
+      <c r="C128">
+        <v>0.9695436989664065</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>0.2247521832119685</v>
+      </c>
+      <c r="C129">
+        <v>0.5365725970910653</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.3881297857995682</v>
+      </c>
+      <c r="C130">
+        <v>1.673529660460104</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>0.955251200781323</v>
+      </c>
+      <c r="C131">
+        <v>-1.136855611931797</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>1.853164719646678</v>
+      </c>
+      <c r="C132">
+        <v>-0.2369391559635313</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.09389340514156053</v>
+      </c>
+      <c r="C133">
+        <v>0.7989453258832279</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>0.7076547440315152</v>
+      </c>
+      <c r="C134">
+        <v>1.265961375941147</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-1.4029002223775</v>
+      </c>
+      <c r="C135">
+        <v>0.5788257343277499</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>0.4459725533178071</v>
+      </c>
+      <c r="C136">
+        <v>1.084538912748011</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-0.9180492081123011</v>
+      </c>
+      <c r="C137">
+        <v>2.058855708208672</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>1.790531491738324</v>
+      </c>
+      <c r="C138">
+        <v>-0.08780239816292401</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>0.6603039218734316</v>
+      </c>
+      <c r="C139">
+        <v>1.119458466650487</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.3666079158416895</v>
+      </c>
+      <c r="C140">
+        <v>-0.632714835792734</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>0.4431340597078079</v>
+      </c>
+      <c r="C141">
+        <v>-0.3421498269233906</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>0.5931089168999227</v>
+      </c>
+      <c r="C142">
+        <v>0.5287695754705806</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>1.426507645325503</v>
+      </c>
+      <c r="C143">
+        <v>1.344803623250635</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-0.5710837532409572</v>
+      </c>
+      <c r="C144">
+        <v>-0.2984252749300699</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>0.7827949900757304</v>
+      </c>
+      <c r="C145">
+        <v>0.1050720639487</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0.4068681312118126</v>
+      </c>
+      <c r="C146">
+        <v>0.6912673631709207</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-2.315021321249556</v>
+      </c>
+      <c r="C147">
+        <v>1.652589166269342</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>-0.7591774459884901</v>
+      </c>
+      <c r="C148">
+        <v>0.2685494546892581</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>-1.23901424071338</v>
+      </c>
+      <c r="C149">
+        <v>0.7485992205550891</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>-1.454606546136431</v>
+      </c>
+      <c r="C150">
+        <v>1.264013704416819</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>-0.1336916481837981</v>
+      </c>
+      <c r="C151">
+        <v>-1.966553926164224</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>0.07713464587171499</v>
+      </c>
+      <c r="C152">
+        <v>-0.3058140251576172</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>1.861284643960648</v>
+      </c>
+      <c r="C153">
+        <v>1.135634618272365</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>-0.5769845555301104</v>
+      </c>
+      <c r="C154">
+        <v>0.6297559657753501</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>0.3926108930197162</v>
+      </c>
+      <c r="C155">
+        <v>-0.700343638365142</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>1.081367487176315</v>
+      </c>
+      <c r="C156">
+        <v>0.763449470120805</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>1.227478026394153</v>
+      </c>
+      <c r="C157">
+        <v>-1.263160824277495</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>0.7387458726593046</v>
+      </c>
+      <c r="C158">
+        <v>-0.3558064269063692</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-1.810965714269817</v>
+      </c>
+      <c r="C159">
+        <v>0.7187968097879316</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>1.159516967864295</v>
+      </c>
+      <c r="C160">
+        <v>0.04704994970362597</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>0.006678124500253645</v>
+      </c>
+      <c r="C161">
+        <v>-0.2367580464204939</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-1.074186950249188</v>
+      </c>
+      <c r="C162">
+        <v>0.5147467716090204</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>2.317475127640628</v>
+      </c>
+      <c r="C163">
+        <v>-0.05698669592674732</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>1.315977547216615</v>
+      </c>
+      <c r="C164">
+        <v>-0.8563169538311389</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>-1.028583172746344</v>
+      </c>
+      <c r="C165">
+        <v>-0.8689545994042456</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>-0.124338701723763</v>
+      </c>
+      <c r="C166">
+        <v>-0.4348615564489449</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-0.4086922157774249</v>
+      </c>
+      <c r="C167">
+        <v>-0.1505769283623808</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>0.7162165093914009</v>
+      </c>
+      <c r="C168">
+        <v>-0.002617103892156469</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>-0.4145581128602912</v>
+      </c>
+      <c r="C169">
+        <v>-0.3975293852154705</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>-0.7801064503952869</v>
+      </c>
+      <c r="C170">
+        <v>1.192262230324474</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>-0.8698094265199989</v>
+      </c>
+      <c r="C171">
+        <v>1.091911667368571</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>-0.9637573525394528</v>
+      </c>
+      <c r="C172">
+        <v>1.869996536360803</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>-0.5464632367473479</v>
+      </c>
+      <c r="C173">
+        <v>-1.055632085367506</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>-0.03656297075191419</v>
+      </c>
+      <c r="C174">
+        <v>-0.8419183099004681</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>-0.1103236846583448</v>
+      </c>
+      <c r="C175">
+        <v>0.9218657923666835</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>0.03286579542421669</v>
+      </c>
+      <c r="C176">
+        <v>1.22805507604591</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>-1.097326575932955</v>
+      </c>
+      <c r="C177">
+        <v>0.5321156872658106</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>0.04818718209176034</v>
+      </c>
+      <c r="C178">
+        <v>-0.1909844182780444</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.599294568860421</v>
+      </c>
+      <c r="C179">
+        <v>-2.095451370769237</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>-0.7077095123890724</v>
+      </c>
+      <c r="C180">
+        <v>-1.368951000146714</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>-0.2893417414021544</v>
+      </c>
+      <c r="C181">
+        <v>0.2380510678661647</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>-0.8237913009971825</v>
+      </c>
+      <c r="C182">
+        <v>0.3461149507620886</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>0.8596612674999091</v>
+      </c>
+      <c r="C183">
+        <v>-0.1836866631015895</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-0.2372382136463663</v>
+      </c>
+      <c r="C184">
+        <v>-0.07458175164587819</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>0.4110019683551552</v>
+      </c>
+      <c r="C185">
+        <v>0.8482511034454872</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>0.8226184033695195</v>
+      </c>
+      <c r="C186">
+        <v>-0.2524552924892561</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-0.1459465587422568</v>
+      </c>
+      <c r="C187">
+        <v>-0.8246403272090397</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-0.2624569638177891</v>
+      </c>
+      <c r="C188">
+        <v>1.300063925331679</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>0.2118108838345061</v>
+      </c>
+      <c r="C189">
+        <v>-1.646606576493637</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>0.4647577101835608</v>
+      </c>
+      <c r="C190">
+        <v>-0.3432608253393195</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>1.745134800578254</v>
+      </c>
+      <c r="C191">
+        <v>-2.20849383753434</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>0.620190240759519</v>
+      </c>
+      <c r="C192">
+        <v>0.8070987240956069</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>-0.4852887042118728</v>
+      </c>
+      <c r="C193">
+        <v>-0.8922083414546186</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>-0.596762728847621</v>
+      </c>
+      <c r="C194">
+        <v>0.3119665828286093</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>-1.911473311558874</v>
+      </c>
+      <c r="C195">
+        <v>-0.007244915841201238</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>-0.3294381355900202</v>
+      </c>
+      <c r="C196">
+        <v>0.7053858985448879</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>0.659833998402787</v>
+      </c>
+      <c r="C197">
+        <v>-1.504975574602195</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.7567114888263355</v>
+      </c>
+      <c r="C198">
+        <v>-0.8960156498342069</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0.6739906687047194</v>
+      </c>
+      <c r="C199">
+        <v>-0.3902908518838926</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>0.8463051610100151</v>
+      </c>
+      <c r="C200">
+        <v>-0.8220375442746721</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-1.137197620586656</v>
+      </c>
+      <c r="C201">
+        <v>0.6614831633042795</v>
       </c>
     </row>
   </sheetData>
